--- a/output/scorecard.xlsx
+++ b/output/scorecard.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +41,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="002C3E50"/>
         <bgColor rgb="002C3E50"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF6B6B"/>
-        <bgColor rgb="00FF6B6B"/>
       </patternFill>
     </fill>
     <fill>
@@ -68,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -492,109 +485,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DORA</t>
+          <t>ISO 27001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ISO 27001</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>12</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NIS2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CBW</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
